--- a/Тест2/264.xlsx
+++ b/Тест2/264.xlsx
@@ -252,19 +252,19 @@
     <t xml:space="preserve">Tuproq uchun inkubatsiya nima uchun bir necha kun davom etishi mumkin?</t>
   </si>
   <si>
-    <t xml:space="preserve">Idish sterillanishi uchun</t>
+    <t xml:space="preserve">Idish sterillanib bo'lishini kutish uchun</t>
   </si>
   <si>
     <t xml:space="preserve">Aktinomitsetlarni hisobga olish uchun</t>
   </si>
   <si>
-    <t xml:space="preserve">Termostat qizishi uchun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viruslarni ko'paytirish uchun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muhit qotishi uchun</t>
+    <t xml:space="preserve">Termostat qizib ketishini kutish uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viruslarni ko'paytirib olish uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muhit qotib qolishini kutish uchun</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Aktinomitsetlarni hisobga olish uchun. Aktinomitsetlarni hisobga olish uchun inkubatsiya bir necha kun davom etishi mumkin. Manba: Mavzu materiali (264.docx); Madigan M.T. va boshq. Brock Biology of Microorganisms, 16-nashr (2021).</t>
